--- a/dados/excel/quadro_escolaridade_categoria.xlsx
+++ b/dados/excel/quadro_escolaridade_categoria.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="D2" s="10" t="n">
         <v>15</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2493835.89</v>
+        <v>2528552.96</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3264.183102094241</v>
+        <v>3271.090504527814</v>
       </c>
     </row>
     <row r="3">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D3" s="14" t="n">
         <v>9</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>1734831.84</v>
+        <v>1747207.46</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>4845.898994413408</v>
+        <v>4853.354055555556</v>
       </c>
     </row>
     <row r="4">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>3100</v>
+        <v>3129</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>64</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>18614875.22</v>
+        <v>18922030.7</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>6004.798458064516</v>
+        <v>6047.309268136784</v>
       </c>
     </row>
     <row r="5">
@@ -905,16 +905,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>3369</v>
+        <v>3411</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>63</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>12489802.53</v>
+        <v>12687062.55</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>3707.272938557435</v>
+        <v>3719.45545294635</v>
       </c>
     </row>
     <row r="6">
@@ -953,16 +953,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>11989</v>
+        <v>12191</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>50957698.26</v>
+        <v>51983148.05</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>4250.371028442739</v>
+        <v>4264.059392174555</v>
       </c>
     </row>
     <row r="8">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>8277</v>
+        <v>8371</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>172</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>37101370.36</v>
+        <v>37661502.63</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>4482.465912770327</v>
+        <v>4499.044633854975</v>
       </c>
     </row>
     <row r="9">
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>822162.34</v>
+        <v>823951.78</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>3045.045703703704</v>
+        <v>3029.234485294118</v>
       </c>
     </row>
     <row r="10">
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>1748</v>
+        <v>1766</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>10968243.51</v>
+        <v>11114406.02</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>6274.738850114416</v>
+        <v>6293.548142695357</v>
       </c>
     </row>
     <row r="12">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>4</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>504991.13</v>
+        <v>512273.81</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>3005.899583333333</v>
+        <v>3013.375352941177</v>
       </c>
     </row>
     <row r="13">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>193425</v>
+        <v>197145</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4467</v>
+        <v>4506</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>911658150.78</v>
+        <v>933597499.51</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4713.238468553703</v>
+        <v>4735.588016485328</v>
       </c>
     </row>
     <row r="15">
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>9360</v>
+        <v>9478</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>18875509.35</v>
+        <v>19148601.74</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>2016.614246794872</v>
+        <v>2020.320926355771</v>
       </c>
     </row>
     <row r="16">
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>20</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>8552571.939999999</v>
+        <v>8690513.449999999</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7193.079848612279</v>
+        <v>7212.044356846473</v>
       </c>
     </row>
     <row r="17">
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>790</v>
+        <v>828</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>7848861.29</v>
+        <v>8237480.95</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>9935.267455696203</v>
+        <v>9948.648490338164</v>
       </c>
     </row>
     <row r="18">
@@ -1217,16 +1217,16 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>4</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>1470421.37</v>
+        <v>1488039.17</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>16338.01522222222</v>
+        <v>16352.07879120879</v>
       </c>
     </row>
     <row r="19">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>52836</v>
+        <v>53673</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>4669</v>
+        <v>4728</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>59520451.38</v>
+        <v>60737712.05999999</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>1126.513198955258</v>
+        <v>1131.625063998659</v>
       </c>
     </row>
     <row r="20">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>11302</v>
+        <v>11463</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>207</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>56749528.52</v>
+        <v>57858618.07</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5021.193463103876</v>
+        <v>5047.423717177005</v>
       </c>
     </row>
     <row r="21">
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="D21" s="14" t="n">
         <v>25</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>5648361.78</v>
+        <v>5692142.43</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>9184.328097560976</v>
+        <v>9195.706672051696</v>
       </c>
     </row>
     <row r="22">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>4</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>1171142.28</v>
+        <v>1206318.78</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>13158.90202247191</v>
+        <v>13112.16065217391</v>
       </c>
     </row>
     <row r="23">
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>272852</v>
+        <v>277658</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>6323</v>
+        <v>6427</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>2226162770.73</v>
+        <v>2277565421.61</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>8158.865504852448</v>
+        <v>8202.772553320992</v>
       </c>
     </row>
     <row r="24">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>32994</v>
+        <v>33513</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>374540852.05</v>
+        <v>382259985.74</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>11351.78675062133</v>
+        <v>11406.31951004088</v>
       </c>
     </row>
     <row r="25">
@@ -1385,16 +1385,16 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>83308</v>
+        <v>85529</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>5714</v>
+        <v>5875</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>164049705.74</v>
+        <v>168960450.35</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>1969.195104191674</v>
+        <v>1975.475573781992</v>
       </c>
     </row>
     <row r="26">
@@ -1409,16 +1409,16 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>7590</v>
+        <v>7773</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>109862610.92</v>
+        <v>112720257.75</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>14474.65229512516</v>
+        <v>14501.51263990737</v>
       </c>
     </row>
     <row r="27">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>17</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>7836352.63</v>
+        <v>7966659.69</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>10137.58425614489</v>
+        <v>10161.55572704082</v>
       </c>
     </row>
     <row r="28">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>127839</v>
+        <v>129632</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>2159</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>1503610249.26</v>
+        <v>1533749445.49</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>11761.74914744327</v>
+        <v>11831.56508801839</v>
       </c>
     </row>
     <row r="29">
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>5020</v>
+        <v>5091</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>79672586.26000001</v>
+        <v>81192895.31</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>15871.03311952191</v>
+        <v>15948.31964447064</v>
       </c>
     </row>
     <row r="30">
@@ -1505,16 +1505,16 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>69</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>15792311.26</v>
+        <v>16018093.35</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>15467.49388834476</v>
+        <v>15476.41869565217</v>
       </c>
     </row>
     <row r="31">
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>8064</v>
+        <v>8242</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>10008079.46</v>
+        <v>10307330.22</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1241.081282242064</v>
+        <v>1250.586049502548</v>
       </c>
     </row>
     <row r="32">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>7</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>786285.4</v>
+        <v>792422.85</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2901.422140221403</v>
+        <v>2902.647802197802</v>
       </c>
     </row>
     <row r="33">
@@ -1577,16 +1577,16 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>7797</v>
+        <v>7917</v>
       </c>
       <c r="D33" s="14" t="n">
         <v>131</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>108744225.24</v>
+        <v>111108174.66</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>13946.93154290111</v>
+        <v>14034.12588859416</v>
       </c>
     </row>
     <row r="34">
@@ -1601,16 +1601,16 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="D34" s="10" t="n">
         <v>14</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>11956740.16</v>
+        <v>12196426.42</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>21124.98261484099</v>
+        <v>21248.12965156794</v>
       </c>
     </row>
     <row r="35">
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>2224</v>
+        <v>2255</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>31770734.29</v>
+        <v>32472907.43</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>14285.40210881295</v>
+        <v>14400.40240798226</v>
       </c>
     </row>
     <row r="38">
